--- a/OSAautoFunction.xlsx
+++ b/OSAautoFunction.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasia/Desktop/GreatUniter/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasia/Desktop/greatuniter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A0159D-B0E7-0E46-BCC6-D6CD5E1693DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95531741-D2AB-1E4E-AAF7-17697224B1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="460" windowWidth="15100" windowHeight="14560" xr2:uid="{5E2F5CD6-290F-304D-9E51-36F1525B1841}"/>
   </bookViews>
@@ -61,9 +61,6 @@
     <t>powerDBm</t>
   </si>
   <si>
-    <t>timecode</t>
-  </si>
-  <si>
     <t>ADC1CH0_VD8_LDD3</t>
   </si>
   <si>
@@ -104,6 +101,9 @@
   </si>
   <si>
     <t>TEMP_CS</t>
+  </si>
+  <si>
+    <t>timecodeHHMMSS</t>
   </si>
 </sst>
 </file>
@@ -531,49 +531,49 @@
         <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
